--- a/dist/成果/防治对象/测量表/360481002211103_桂林村桂林桥01/沟道纵断面成果表_AFAE90012D000000ZACS002.xlsx
+++ b/dist/成果/防治对象/测量表/360481002211103_桂林村桂林桥01/沟道纵断面成果表_AFAE90012D000000ZACS002.xlsx
@@ -822,7 +822,7 @@
         <v>18.1</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>18.53000208390399</v>
+        <v>18.4539400647697</v>
       </c>
       <c r="G12" s="23" t="n">
         <v>115.614229</v>
@@ -850,7 +850,7 @@
         <v>18.009</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>18.0377776783394</v>
+        <v>18.03909958156605</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>115.614468</v>
@@ -878,7 +878,7 @@
         <v>17.978</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>18.33178520007548</v>
+        <v>18.01426671512844</v>
       </c>
       <c r="G14" s="23" t="n">
         <v>115.614728</v>
@@ -906,7 +906,7 @@
         <v>17.778</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>18.12798547604434</v>
+        <v>17.94279673138007</v>
       </c>
       <c r="G15" s="23" t="n">
         <v>115.615123</v>
@@ -934,7 +934,7 @@
         <v>17.682</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>17.6973140373733</v>
+        <v>17.71009016898369</v>
       </c>
       <c r="G16" s="23" t="n">
         <v>115.615529</v>
@@ -962,7 +962,7 @@
         <v>17.628</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>17.9930891458846</v>
+        <v>17.98806568174768</v>
       </c>
       <c r="G17" s="23" t="n">
         <v>115.616138</v>
@@ -990,7 +990,7 @@
         <v>17.598</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>17.97521390708555</v>
+        <v>17.82130499047743</v>
       </c>
       <c r="G18" s="23" t="n">
         <v>115.616274</v>
@@ -1018,7 +1018,7 @@
         <v>17.463</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>17.97057506610412</v>
+        <v>17.49482210067236</v>
       </c>
       <c r="G19" s="23" t="n">
         <v>115.616912</v>
@@ -1046,7 +1046,7 @@
         <v>17.46</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>17.87047242593069</v>
+        <v>17.89229013741556</v>
       </c>
       <c r="G20" s="23" t="n">
         <v>115.617049</v>
@@ -1074,7 +1074,7 @@
         <v>17.347</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>17.74556896261829</v>
+        <v>17.6969759197329</v>
       </c>
       <c r="G21" s="23" t="n">
         <v>115.617231</v>
@@ -1102,7 +1102,7 @@
         <v>17.309</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>17.80391988730779</v>
+        <v>17.65904672700113</v>
       </c>
       <c r="G22" s="23" t="n">
         <v>115.61744</v>
@@ -1130,7 +1130,7 @@
         <v>17.274</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>17.7912129139771</v>
+        <v>17.58529708273001</v>
       </c>
       <c r="G23" s="23" t="n">
         <v>115.617798</v>
@@ -1158,7 +1158,7 @@
         <v>17.264</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>17.3295942052942</v>
+        <v>17.49855494607502</v>
       </c>
       <c r="G24" s="23" t="n">
         <v>115.618342</v>
@@ -1186,7 +1186,7 @@
         <v>17.195</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>17.52332353554364</v>
+        <v>17.43531591567357</v>
       </c>
       <c r="G25" s="23" t="n">
         <v>115.618397</v>
@@ -1214,7 +1214,7 @@
         <v>17.183</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>17.32739724453288</v>
+        <v>17.43416055903637</v>
       </c>
       <c r="G26" s="23" t="n">
         <v>115.619018</v>
@@ -1242,7 +1242,7 @@
         <v>17.169</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>17.2244100433156</v>
+        <v>17.26269989973671</v>
       </c>
       <c r="G27" s="23" t="n">
         <v>115.619331</v>
@@ -1270,7 +1270,7 @@
         <v>17.164</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>17.19343712331476</v>
+        <v>17.54768795903278</v>
       </c>
       <c r="G28" s="23" t="n">
         <v>115.619585</v>
@@ -1298,7 +1298,7 @@
         <v>17.153</v>
       </c>
       <c r="F29" s="22" t="n">
-        <v>17.24766637530315</v>
+        <v>17.45874419612554</v>
       </c>
       <c r="G29" s="23" t="n">
         <v>115.619927</v>
@@ -1326,7 +1326,7 @@
         <v>17.144</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>17.53098202717618</v>
+        <v>17.14831026386965</v>
       </c>
       <c r="G30" s="23" t="n">
         <v>115.620445</v>
@@ -1354,7 +1354,7 @@
         <v>16.703</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>17.48863777085174</v>
+        <v>16.72331308055577</v>
       </c>
       <c r="G31" s="23" t="n">
         <v>115.62095</v>
@@ -1382,7 +1382,7 @@
         <v>16.66</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>17.38536547423663</v>
+        <v>16.82997642829638</v>
       </c>
       <c r="G32" s="23" t="n">
         <v>115.621194</v>
@@ -1410,7 +1410,7 @@
         <v>16.372</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>17.11226583181998</v>
+        <v>16.43557991626998</v>
       </c>
       <c r="G33" s="23" t="n">
         <v>115.621619</v>
@@ -1438,7 +1438,7 @@
         <v>16.232</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>16.64539995572969</v>
+        <v>16.41383101777746</v>
       </c>
       <c r="G34" s="23" t="n">
         <v>115.62206</v>
@@ -1462,16 +1462,16 @@
     <mergeCell ref="D3:H3"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D2:H2" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"A,B"</formula1>
     </dataValidation>
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
-    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"85高程系,假定高程系"</formula1>
     </dataValidation>
-    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="D7:H7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"水准仪／卷尺测量法,GNSS RTK测量法,全站仪法,三维激光扫描方法"</formula1>
     </dataValidation>
   </dataValidations>
